--- a/ci-build/ValueSet-onko-therapy-phase.xlsx
+++ b/ci-build/ValueSet-onko-therapy-phase.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T15:05:40+00:00</t>
+    <t>2026-07-27T15:55:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-phase.xlsx
+++ b/ci-build/ValueSet-onko-therapy-phase.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:55:12+00:00</t>
+    <t>2026-07-28T00:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-phase.xlsx
+++ b/ci-build/ValueSet-onko-therapy-phase.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T00:29:57+00:00</t>
+    <t>2026-07-28T09:41:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-phase.xlsx
+++ b/ci-build/ValueSet-onko-therapy-phase.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T09:41:52+00:00</t>
+    <t>2026-07-29T10:30:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-phase.xlsx
+++ b/ci-build/ValueSet-onko-therapy-phase.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T10:30:12+00:00</t>
+    <t>2026-07-29T11:12:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-phase.xlsx
+++ b/ci-build/ValueSet-onko-therapy-phase.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T11:12:20+00:00</t>
+    <t>2026-07-29T12:00:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-phase.xlsx
+++ b/ci-build/ValueSet-onko-therapy-phase.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:36:35+00:00</t>
+    <t>2026-07-30T15:22:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-phase.xlsx
+++ b/ci-build/ValueSet-onko-therapy-phase.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T15:22:14+00:00</t>
+    <t>2026-07-31T08:51:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-phase.xlsx
+++ b/ci-build/ValueSet-onko-therapy-phase.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T08:51:02+00:00</t>
+    <t>2026-07-31T12:16:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,8 +87,9 @@
     <t>Sequenzielle Phase (Unter-Intention) innerhalb eines Behandlungskonzepts – ergänzend zur
 Haupt-Therapieintention. In SNOMED CT liegen diese Konzepte nicht in der Intent-Hierarchie,
 sondern als Behandlungsformen unter `716872004 | Antineoplastic chemotherapy regimen`.
-Deutsche Anzeigetexte als Concept-Display. Extensible gebunden (z. B. Konsolidierung
-ergänzbar).</t>
+Als Concept-Display dient der englische SNOMED-Anzeigetext des aktuellen Release; die deutschen
+Begriffe stehen in den Label-Texten des Leitfadens. Extensible gebunden (z. B.
+Konsolidierung ergänzbar).</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -109,25 +110,25 @@
     <t>450827009</t>
   </si>
   <si>
-    <t>Induktionstherapie</t>
+    <t>Induction chemotherapy</t>
   </si>
   <si>
     <t>816151001</t>
   </si>
   <si>
-    <t>Konsolidierungstherapie</t>
+    <t>Consolidation antineoplastic chemotherapy</t>
   </si>
   <si>
     <t>1254741007</t>
   </si>
   <si>
-    <t>Intensivierungstherapie</t>
+    <t>Intensification antineoplastic therapy regimen</t>
   </si>
   <si>
     <t>1345242003</t>
   </si>
   <si>
-    <t>Erhaltungstherapie</t>
+    <t>Maintenance antineoplastic therapy</t>
   </si>
   <si>
     <t/>

--- a/ci-build/ValueSet-onko-therapy-phase.xlsx
+++ b/ci-build/ValueSet-onko-therapy-phase.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:16:37+00:00</t>
+    <t>2026-07-31T12:21:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-phase.xlsx
+++ b/ci-build/ValueSet-onko-therapy-phase.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:21:47+00:00</t>
+    <t>2026-07-31T12:58:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-phase.xlsx
+++ b/ci-build/ValueSet-onko-therapy-phase.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:58:15+00:00</t>
+    <t>2026-07-31T13:16:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-phase.xlsx
+++ b/ci-build/ValueSet-onko-therapy-phase.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:16:40+00:00</t>
+    <t>2026-07-31T13:26:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-phase.xlsx
+++ b/ci-build/ValueSet-onko-therapy-phase.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:26:52+00:00</t>
+    <t>2026-07-31T13:33:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-phase.xlsx
+++ b/ci-build/ValueSet-onko-therapy-phase.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:33:02+00:00</t>
+    <t>2026-07-31T13:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-phase.xlsx
+++ b/ci-build/ValueSet-onko-therapy-phase.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:38:59+00:00</t>
+    <t>2026-07-31T13:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-phase.xlsx
+++ b/ci-build/ValueSet-onko-therapy-phase.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:45:11+00:00</t>
+    <t>2026-07-31T14:14:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-phase.xlsx
+++ b/ci-build/ValueSet-onko-therapy-phase.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T14:14:54+00:00</t>
+    <t>2026-07-31T14:25:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-phase.xlsx
+++ b/ci-build/ValueSet-onko-therapy-phase.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T14:25:45+00:00</t>
+    <t>2026-08-02T18:42:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-phase.xlsx
+++ b/ci-build/ValueSet-onko-therapy-phase.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-02T18:42:01+00:00</t>
+    <t>2026-08-02T18:51:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-phase.xlsx
+++ b/ci-build/ValueSet-onko-therapy-phase.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-02T18:51:55+00:00</t>
+    <t>2026-08-03T05:20:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
